--- a/旅人键位配置.xlsx
+++ b/旅人键位配置.xlsx
@@ -718,7 +718,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>空格</t>
+          <t>鼠标右键</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -731,7 +731,11 @@
           <t>否</t>
         </is>
       </c>
-      <c r="J5" s="3" t="inlineStr"/>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>方案B：右键=闪避（原神/鸣潮习惯）</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -965,12 +969,12 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Q</t>
+          <t>E</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>鼠标右键</t>
+          <t>Ctrl</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -983,7 +987,11 @@
           <t>否</t>
         </is>
       </c>
-      <c r="J10" s="3" t="inlineStr"/>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>方案A：拔刀态按 E 纳刀（与使用道具同键）；方案B：Ctrl</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1530,7 +1538,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Tab</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1543,7 +1551,11 @@
           <t>否</t>
         </is>
       </c>
-      <c r="J21" s="3" t="inlineStr"/>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>方案B：Tab=锁定（鸣潮习惯）</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1573,17 +1585,17 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>按住B + 滚轮</t>
+          <t>按住B + 鼠标移动</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>按住B + 滚轮</t>
+          <t>按住Tab + 鼠标移动</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>按住+滚轮</t>
+          <t>按住+移动鼠标</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1591,7 +1603,11 @@
           <t>否</t>
         </is>
       </c>
-      <c r="J22" s="3" t="inlineStr"/>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>按住锁定键滑动鼠标，圆形轮盘选择多目标（对应手柄推右摇杆）</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1626,7 +1642,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>按住B + 滚轮</t>
+          <t>按住Tab + 滚轮</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -1787,7 +1803,11 @@
           <t>否</t>
         </is>
       </c>
-      <c r="J26" s="3" t="inlineStr"/>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>方案A：纳刀态按 E 使用默认道具（与纳刀同键）</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -2022,7 +2042,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>按住Tab + 滚轮</t>
+          <t>长按T + 滚轮</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2035,7 +2055,11 @@
           <t>否</t>
         </is>
       </c>
-      <c r="J31" s="3" t="inlineStr"/>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>方案B：长按 T 呼出轮盘（鸣潮探索工具轮盘习惯）</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
